--- a/public/resume/職務経歴書_劉洋.xlsx
+++ b/public/resume/職務経歴書_劉洋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lijiao/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913637F7-38B5-BA48-8BE5-47D4D4D7138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55D8D2-2CD8-574F-AED7-8325059E948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="600" windowWidth="31360" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,16 +91,6 @@
     <phoneticPr fontId="29"/>
   </si>
   <si>
-    <t>[プロジェクト要員]
-構築フェーズ（〜2023.6 /15名体制）
-運用(6名)
-[実績]
-・既存解析をもとにシステムアーキテクチャを設計
-・1億件照合処理を4時間→35分へ短縮
-・AWS連携基盤、SSO統合、少人数運用体制への移行を推進</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
     <t xml:space="preserve">[プロジェクト名]
 YAMATO（ヤマト運輸）— 集荷・決済システム
 [概要]
@@ -108,16 +98,6 @@
 [担当フェーズ]
 設計から開発・テスト・リリースまでを担当
 </t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>[プロジェクト要員]
-15名
-[実績]
-・PayPay決済APIを統合し決済手段を追加
-・OTP認証を導入しセキュリティを強化
-・上門集荷業務ロジックを設計・実装
-・新人の設計・コードレビューを担当</t>
     <phoneticPr fontId="29"/>
   </si>
   <si>
@@ -214,19 +194,6 @@
     <phoneticPr fontId="29"/>
   </si>
   <si>
-    <t>[プロジェクト要員]
-構築フェーズ（〜2023.6 /15名体制）
-運用(6名)
-[実績]
-・バックエンド唯一担当として技術選定～実装を担当
-・REST API基盤を構築
-・SQS／SNSによる非同期通知基盤を実装
-・Redis導入で応答性能を改善
-・OpenAPI導入で開発・引継ぎを効率化
-・10店舗以上への展開を支援</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
     <t xml:space="preserve">[プロジェクト名]
 複数政府系プロジェクト
 [概要]
@@ -249,24 +216,6 @@
 Spring
 Quartz
 Oracle</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>[プロジェクト要員]
-6人
-[実績]
-・Dubbo＋ZookeeperでSOA基盤を構築
-・主要機能をサービス分割し疎結合化を実現
-・検索、セッション管理、非同期処理基盤を整備</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>[プロジェクト要員]
-8名
-[実績]
-・GPS・バッテリー・走行ログの収集・蓄積基盤を設計・実装
-・監視・分析向け業務システムの開発を担当
-・グループ4社のPHEV車両への導入を実現</t>
     <phoneticPr fontId="29"/>
   </si>
   <si>
@@ -350,6 +299,67 @@
 さらに、社内での技術共有や研修にも携わっており、単に自分で実装するだけでなく、周囲にわかりやすく伝え、チーム全体の開発力向上に貢献できる点も強みです。既存システムの改善から新規開発まで、技術と業務の両面を意識しながら柔軟に価値提供していきたいと考えております。
 個人開発の成果物は個人サイトにて公開しております。
 個人サイト：liuyang19900520.com</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>[プロジェクト要員]
+構築フェーズ（〜2023.6 /15名体制）
+運用(6名)
+[役割]
+SE
+[実績]
+・既存解析をもとにシステムアーキテクチャを設計
+・1億件照合処理を4時間→35分へ短縮
+・AWS連携基盤、SSO統合、少人数運用体制への移行を推進</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>[プロジェクト要員]
+15名
+[役割]
+SE
+[実績]
+・PayPay決済APIを統合し決済手段を追加
+・OTP認証を導入しセキュリティを強化
+・上門集荷業務ロジックを設計・実装
+・新人の設計・コードレビューを担当</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>[プロジェクト要員]
+構築フェーズ（〜2023.6 /15名体制）
+運用(6名)
+[役割]
+SE
+[実績]
+・バックエンド唯一担当として技術選定～実装を担当
+・REST API基盤を構築
+・SQS／SNSによる非同期通知基盤を実装
+・Redis導入で応答性能を改善
+・OpenAPI導入で開発・引継ぎを効率化
+・10店舗以上への展開を支援</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>[プロジェクト要員]
+6人
+[役割]
+TL
+[実績]
+・Dubbo＋ZookeeperでSOA基盤を構築
+・主要機能をサービス分割し疎結合化を実現
+・検索、セッション管理、非同期処理基盤を整備</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>[プロジェクト要員]
+8名
+[役割]
+PG→SE
+[実績]
+・GPS・バッテリー・走行ログの収集・蓄積基盤を設計・実装
+・監視・分析向け業務システムの開発を担当
+・グループ4社のPHEV車両への導入を実現</t>
     <phoneticPr fontId="29"/>
   </si>
 </sst>
@@ -1197,6 +1207,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1206,53 +1225,44 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1694,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
@@ -1704,114 +1714,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A1" s="26"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="16">
       <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="17"/>
+      <c r="C4" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="A5" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1">
-      <c r="A6" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
     </row>
     <row r="7" spans="1:4" ht="27.5" customHeight="1">
-      <c r="A7" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31"/>
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" ht="85" customHeight="1" thickBot="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="34"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="14" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="A10" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1">
       <c r="A17" s="5" t="s">
@@ -1831,824 +1841,860 @@
       <c r="A18" s="13">
         <v>44501</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>14</v>
+      <c r="C18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="8"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="8"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="8"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="8"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="8"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="8"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="8"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" thickBot="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="13">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="8"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" thickBot="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="13">
         <v>43617</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="21" t="s">
+      <c r="B31" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="7" t="s">
+      <c r="D31" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="13">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="13">
         <v>44470</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="7"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="8"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="8"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="8"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="8"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="8"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="8"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" thickBot="1">
-      <c r="A40" s="9"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="8"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="13">
-        <v>42948</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+    </row>
+    <row r="42" spans="1:4" ht="15" thickBot="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="13">
+        <v>42948</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="13">
         <v>43617</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="7"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="8"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="8"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="8"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="8"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="8"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="8"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="8"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="8"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="8"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-    </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1">
-      <c r="A54" s="9"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="8"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="14"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-    </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1">
-      <c r="A56" s="20" t="s">
-        <v>21</v>
-      </c>
+      <c r="A55" s="8"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="8"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:4">
+      <c r="A57" s="8"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+    </row>
+    <row r="58" spans="1:4" ht="15" thickBot="1">
+      <c r="A58" s="9"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+    </row>
+    <row r="60" spans="1:4" ht="15" thickBot="1">
+      <c r="A60" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+    </row>
+    <row r="61" spans="1:4" ht="15" thickBot="1">
+      <c r="A61" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B61" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C61" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D61" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="13">
+    <row r="62" spans="1:4">
+      <c r="A62" s="13">
         <v>42552</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="7" t="s">
+      <c r="B62" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="13">
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="13">
         <v>42856</v>
       </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="7"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="8"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="8"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="8"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="8"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="8"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="8"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="8"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-    </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1">
-      <c r="A69" s="9"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="8"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="13">
+      <c r="A70" s="8"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="8"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="8"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="8"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+    </row>
+    <row r="74" spans="1:4" ht="15" thickBot="1">
+      <c r="A74" s="9"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="13">
         <v>41791</v>
       </c>
-      <c r="B70" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="7" t="s">
+      <c r="B75" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="13">
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="13">
         <v>42522</v>
       </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="7"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="8"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="8"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="8"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="8"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="8"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
+      <c r="A78" s="13"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="8"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-    </row>
-    <row r="80" spans="1:4" ht="15" thickBot="1">
-      <c r="A80" s="9"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="8"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="13">
-        <v>41426</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="13">
-        <v>41760</v>
-      </c>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
+      <c r="A83" s="8"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="7"/>
-      <c r="B84" s="22"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="8"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="22"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
     </row>
     <row r="86" spans="1:4" ht="15" thickBot="1">
       <c r="A86" s="9"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
+      <c r="A87" s="13">
+        <v>41426</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="16" t="s">
-        <v>38</v>
+      <c r="A88" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="16" t="s">
-        <v>39</v>
+      <c r="A89" s="13">
+        <v>41760</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="17"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="16" t="s">
-        <v>40</v>
-      </c>
+      <c r="A90" s="7"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="16" t="s">
-        <v>41</v>
-      </c>
+      <c r="A91" s="8"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
     </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="16" t="s">
+    <row r="92" spans="1:4" ht="15" thickBot="1">
+      <c r="A92" s="9"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="20"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="20"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="20"/>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="10"/>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="18" t="s">
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="20"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="20"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="10"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="16" t="s">
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="17"/>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B101" s="17"/>
-      <c r="C101" s="17"/>
-      <c r="D101" s="17"/>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="16" t="s">
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104" s="20"/>
+      <c r="C104" s="20"/>
+      <c r="D104" s="20"/>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B105" s="20"/>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" s="20"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" s="20"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" s="20"/>
+      <c r="C108" s="20"/>
+      <c r="D108" s="20"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="11"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" s="20"/>
+      <c r="C110" s="20"/>
+      <c r="D110" s="20"/>
+    </row>
+    <row r="111" spans="1:4" ht="193" customHeight="1">
+      <c r="A111" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="11"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B104" s="17"/>
-      <c r="C104" s="17"/>
-      <c r="D104" s="17"/>
-    </row>
-    <row r="105" spans="1:4" ht="193" customHeight="1">
-      <c r="A105" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="17"/>
-    </row>
-    <row r="106" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A106" s="16"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="17"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="16"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="17"/>
-      <c r="D110" s="17"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="3"/>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="16"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="17"/>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="16"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="17"/>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="16"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="17"/>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="16"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
+      <c r="B111" s="20"/>
+      <c r="C111" s="20"/>
+      <c r="D111" s="20"/>
+    </row>
+    <row r="112" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A112" s="19"/>
+      <c r="B112" s="20"/>
+      <c r="C112" s="20"/>
+      <c r="D112" s="20"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="16"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="17"/>
+      <c r="A116" s="19"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
+      <c r="D116" s="20"/>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="16"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="17"/>
+      <c r="A117" s="3"/>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="16"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="17"/>
+      <c r="A118" s="19"/>
+      <c r="B118" s="20"/>
+      <c r="C118" s="20"/>
+      <c r="D118" s="20"/>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="3"/>
+      <c r="A119" s="19"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="20"/>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="16"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
+      <c r="A120" s="19"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="20"/>
+      <c r="D120" s="20"/>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="16"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
+      <c r="A121" s="19"/>
+      <c r="B121" s="20"/>
+      <c r="C121" s="20"/>
+      <c r="D121" s="20"/>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="16"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="17"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="20"/>
+      <c r="C122" s="20"/>
+      <c r="D122" s="20"/>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="16"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="17"/>
-      <c r="D123" s="17"/>
+      <c r="A123" s="19"/>
+      <c r="B123" s="20"/>
+      <c r="C123" s="20"/>
+      <c r="D123" s="20"/>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="16"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="17"/>
+      <c r="A124" s="19"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="20"/>
+      <c r="D124" s="20"/>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="16"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="17"/>
-      <c r="D125" s="17"/>
+      <c r="A125" s="3"/>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="16"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="17"/>
-      <c r="D126" s="17"/>
+      <c r="A126" s="19"/>
+      <c r="B126" s="20"/>
+      <c r="C126" s="20"/>
+      <c r="D126" s="20"/>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="4"/>
+      <c r="A127" s="19"/>
+      <c r="B127" s="20"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="16"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="17"/>
-      <c r="D128" s="17"/>
+      <c r="A128" s="19"/>
+      <c r="B128" s="20"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="16"/>
-      <c r="B129" s="17"/>
-      <c r="C129" s="17"/>
-      <c r="D129" s="17"/>
+      <c r="A129" s="19"/>
+      <c r="B129" s="20"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="3"/>
+      <c r="A130" s="19"/>
+      <c r="B130" s="20"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="19"/>
+      <c r="B131" s="20"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="19"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="4"/>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="19"/>
+      <c r="B134" s="20"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="19"/>
+      <c r="B135" s="20"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B81:B86"/>
-    <mergeCell ref="C81:C86"/>
-    <mergeCell ref="D81:D86"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A112:D112"/>
     <mergeCell ref="A93:D93"/>
     <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A95:D95"/>
     <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A7:D8"/>
-    <mergeCell ref="D58:D69"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="C70:C80"/>
-    <mergeCell ref="D70:D80"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A126:D126"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="C43:C58"/>
+    <mergeCell ref="D43:D58"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="B58:B69"/>
-    <mergeCell ref="C58:C69"/>
+    <mergeCell ref="A7:D8"/>
+    <mergeCell ref="D62:D74"/>
+    <mergeCell ref="B75:B86"/>
+    <mergeCell ref="C75:C86"/>
+    <mergeCell ref="D75:D86"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="B62:B74"/>
+    <mergeCell ref="C62:C74"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B18:B29"/>
-    <mergeCell ref="C18:C29"/>
-    <mergeCell ref="D18:D29"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="C30:C40"/>
-    <mergeCell ref="D30:D40"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="C41:C54"/>
-    <mergeCell ref="D41:D54"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="B18:B30"/>
+    <mergeCell ref="C18:C30"/>
+    <mergeCell ref="D18:D30"/>
+    <mergeCell ref="B31:B42"/>
+    <mergeCell ref="C31:C42"/>
+    <mergeCell ref="D31:D42"/>
+    <mergeCell ref="B43:B58"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="C87:C92"/>
+    <mergeCell ref="D87:D92"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A104:D104"/>
     <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A129:D129"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/resume/職務経歴書_劉洋.xlsx
+++ b/public/resume/職務経歴書_劉洋.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lijiao/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55D8D2-2CD8-574F-AED7-8325059E948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B53F99-5F7D-1C47-8D1D-C34E02BE9EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="600" windowWidth="31360" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_Hlk105069501" localSheetId="0">編年体_職務経歴書サンプル_sample_chronology!$C$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">編年体_職務経歴書サンプル_sample_chronology!$A$1:$D$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">編年体_職務経歴書サンプル_sample_chronology!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -110,39 +110,6 @@
     <phoneticPr fontId="29"/>
   </si>
   <si>
-    <t>Spring Boot
-Shell
-PostgreSQL
-Procedure
-Windows Server Azure</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>Spring Boot
-Spring Batch
-Shell
-Aurora
-Procedure
-EC2
-S3
-Lambda
-など</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>Spring Boot
-NestJs
-Vue2.x
-MySQL
-Redis
-EC2
-S3
-SQS
-SNS
-など</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
     <t>勤務先名：スナオ株式会社      　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　（勤務期間：2013年7月～2017年5月）</t>
     <phoneticPr fontId="29"/>
   </si>
@@ -168,18 +135,6 @@
   </si>
   <si>
     <t>・生成AI×Cloudの個人プロダクトを継続開発・公開し、技術検証を継続している</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>Dubbo
-Zookeeper
-Spring
-MySQL
-Redis
-SolrCloud
-FastDFS
-ActiveMQ
-Nginx</t>
     <phoneticPr fontId="29"/>
   </si>
   <si>
@@ -209,13 +164,6 @@
 [担当フェーズ]
 設計から開発・テスト・リリースまでを担当
 </t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>Struts2
-Spring
-Quartz
-Oracle</t>
     <phoneticPr fontId="29"/>
   </si>
   <si>
@@ -236,12 +184,6 @@
     <phoneticPr fontId="29"/>
   </si>
   <si>
-    <t>複雑な既存基幹システムの制約を踏まえ、実装性・運用性を考慮した再構築方針の立案と、システムアーキテクチャ設計に従事してまいりました。既存システム解析、技術選定、設計、実装、リリース、運用定着まで一貫して担当した経験があります。
-Java / Springを中心に、API開発、Batch処理、データ連携、DB設計、クラウド活用まで幅広く対応可能です。
-また、個人開発ではフロントエンドからバックエンド、インフラまで一通り経験しており、フルスタックでの開発にも対応できます。複雑な業務要件や多くの制約がある環境においても、少人数体制で新規開発および継続改善を自走して推進し、新人育成や設計・コードレビューにも携わってきました。</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
     <t>・OS：Windows、Linux</t>
     <phoneticPr fontId="29"/>
   </si>
@@ -283,10 +225,6 @@
   </si>
   <si>
     <t>氏名：劉　洋　</t>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2026年3月35日現在         </t>
     <phoneticPr fontId="29"/>
   </si>
   <si>
@@ -360,6 +298,76 @@
 ・GPS・バッテリー・走行ログの収集・蓄積基盤を設計・実装
 ・監視・分析向け業務システムの開発を担当
 ・グループ4社のPHEV車両への導入を実現</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年3月25日現在         </t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>Java
+Spring Boot
+Shell
+PostgreSQL
+Procedure
+Windows Server Azure
+など</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>複雑な既存基幹システムの制約を踏まえ、実装性・運用性・安全性を考慮した再構築方針の立案と、システムアーキテクチャ設計に従事してまいりました。既存システム解析、技術選定、設計、実装、リリース、運用定着まで一貫して担当した経験があります。
+Java / Springを中心に、API開発、Batch処理、データ連携、DB設計、クラウド活用まで幅広く対応可能です。
+また、個人開発ではフロントエンドからバックエンド、インフラまで一通り経験しており、フルスタックでの開発にも対応できます。複雑な業務要件や多くの制約がある環境においても、少人数体制で新規開発および継続改善を自走して推進し、新人育成や設計・コードレビューにも携わってきました。</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>Java
+Struts2
+Spring
+Quartz
+Oracle</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>Java
+Dubbo
+Zookeeper
+Spring
+MySQL
+Redis
+SolrCloud
+FastDFS
+ActiveMQ
+Nginx</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>Java
+Python
+Spring Boot
+Spring Batch
+Shell
+Aurora
+Procedure
+EC2
+S3
+Lambda
+など</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>Java Typescript
+Python
+Spring Boot
+NestJs
+Vue2.x
+MySQL
+Redis
+EC2
+S3
+SQS
+SNS
+など</t>
     <phoneticPr fontId="29"/>
   </si>
 </sst>
@@ -1158,7 +1166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1243,6 +1251,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1255,14 +1272,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="57" fontId="22" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1704,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
@@ -1714,7 +1725,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A1" s="28"/>
+      <c r="A1" s="31"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -1723,7 +1734,7 @@
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="17.25" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="20"/>
@@ -1734,30 +1745,30 @@
       <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>44</v>
+      <c r="C4" s="33" t="s">
+        <v>45</v>
       </c>
       <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="30" t="s">
-        <v>43</v>
+      <c r="A5" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1">
-      <c r="A6" s="31" t="s">
-        <v>31</v>
+      <c r="A6" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" customHeight="1">
+    <row r="7" spans="1:4" ht="37" customHeight="1">
       <c r="A7" s="22" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
@@ -1773,16 +1784,16 @@
       <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="14" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="A10" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -1790,7 +1801,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -1798,7 +1809,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -1808,7 +1819,7 @@
       <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="20"/>
@@ -1816,7 +1827,7 @@
       <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="20"/>
@@ -1845,10 +1856,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1935,10 +1946,10 @@
         <v>14</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2012,17 +2023,17 @@
       <c r="D42" s="18"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13">
+      <c r="A43" s="35">
         <v>42948</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2126,8 +2137,8 @@
       <c r="D59" s="15"/>
     </row>
     <row r="60" spans="1:4" ht="15" thickBot="1">
-      <c r="A60" s="32" t="s">
-        <v>19</v>
+      <c r="A60" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -2152,13 +2163,13 @@
         <v>42552</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2242,13 +2253,13 @@
         <v>41791</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2326,7 +2337,7 @@
         <v>41426</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
@@ -2353,21 +2364,23 @@
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
     </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="8"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-    </row>
-    <row r="92" spans="1:4" ht="15" thickBot="1">
-      <c r="A92" s="9"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
+    <row r="91" spans="1:4" ht="15" thickBot="1">
+      <c r="A91" s="9"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="21" t="s">
-        <v>7</v>
+      <c r="A93" s="19" t="s">
+        <v>27</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -2375,7 +2388,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -2383,7 +2396,7 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -2391,7 +2404,7 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -2399,7 +2412,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -2407,7 +2420,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -2415,26 +2428,26 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
+      <c r="A100" s="10"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="10"/>
+      <c r="A101" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="21" t="s">
-        <v>8</v>
+      <c r="A102" s="19" t="s">
+        <v>19</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -2442,7 +2455,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -2450,7 +2463,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -2458,7 +2471,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -2466,7 +2479,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -2474,53 +2487,51 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
       <c r="D107" s="20"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B108" s="20"/>
-      <c r="C108" s="20"/>
-      <c r="D108" s="20"/>
+      <c r="A108" s="11"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="11"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="21" t="s">
+      <c r="A109" s="21" t="s">
         <v>9</v>
+      </c>
+      <c r="B109" s="20"/>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+    </row>
+    <row r="110" spans="1:4" ht="193" customHeight="1">
+      <c r="A110" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
       <c r="D110" s="20"/>
     </row>
-    <row r="111" spans="1:4" ht="193" customHeight="1">
-      <c r="A111" s="19" t="s">
-        <v>46</v>
-      </c>
+    <row r="111" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
       <c r="D111" s="20"/>
     </row>
-    <row r="112" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A112" s="19"/>
-      <c r="B112" s="20"/>
-      <c r="C112" s="20"/>
-      <c r="D112" s="20"/>
+    <row r="115" spans="1:4">
+      <c r="A115" s="19"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="19"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
+      <c r="A116" s="3"/>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="3"/>
+      <c r="A117" s="19"/>
+      <c r="B117" s="20"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="20"/>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
@@ -2559,13 +2570,13 @@
       <c r="D123" s="20"/>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="19"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
+      <c r="A124" s="3"/>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="3"/>
+      <c r="A125" s="19"/>
+      <c r="B125" s="20"/>
+      <c r="C125" s="20"/>
+      <c r="D125" s="20"/>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
@@ -2604,13 +2615,13 @@
       <c r="D131" s="20"/>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="19"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
+      <c r="A132" s="4"/>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="4"/>
+      <c r="A133" s="19"/>
+      <c r="B133" s="20"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
@@ -2619,43 +2630,37 @@
       <c r="D134" s="20"/>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="19"/>
-      <c r="B135" s="20"/>
-      <c r="C135" s="20"/>
-      <c r="D135" s="20"/>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="3"/>
+      <c r="A135" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="A129:D129"/>
     <mergeCell ref="A130:D130"/>
     <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A133:D133"/>
     <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A109:D109"/>
     <mergeCell ref="A110:D110"/>
     <mergeCell ref="A111:D111"/>
-    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A93:D93"/>
     <mergeCell ref="A94:D94"/>
     <mergeCell ref="A95:D95"/>
     <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A106:D106"/>
     <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A127:D127"/>
     <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A117:D117"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A119:D119"/>
     <mergeCell ref="A120:D120"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="A122:D122"/>
     <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A125:D125"/>
     <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A127:D127"/>
     <mergeCell ref="C43:C58"/>
     <mergeCell ref="D43:D58"/>
     <mergeCell ref="A11:D11"/>
@@ -2684,20 +2689,23 @@
     <mergeCell ref="C31:C42"/>
     <mergeCell ref="D31:D42"/>
     <mergeCell ref="B43:B58"/>
-    <mergeCell ref="B87:B92"/>
-    <mergeCell ref="C87:C92"/>
-    <mergeCell ref="D87:D92"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A98:D98"/>
     <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A103:D103"/>
     <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A105:D105"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="91" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="42" max="3" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>